--- a/.claude/skills/viabilidad-prerelleno/assets/plantilla_informe_viabilidad.xlsx
+++ b/.claude/skills/viabilidad-prerelleno/assets/plantilla_informe_viabilidad.xlsx
@@ -1479,7 +1479,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
     <dxf>
       <font>
         <b val="1"/>
@@ -1507,6 +1507,27 @@
         <b val="1"/>
         <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -9423,8 +9444,22 @@
       <formula>$E$21="rojo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <conditionalFormatting sqref="E22:H22">
+    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="0">
+      <formula>$E$22="verde"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="0">
+      <formula>$E$22="amarillo"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="0">
+      <formula>$E$22="rojo"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
     <dataValidation sqref="E21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"verde,amarillo,rojo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"verde,amarillo,rojo"</formula1>
     </dataValidation>
   </dataValidations>

--- a/.claude/skills/viabilidad-prerelleno/assets/plantilla_informe_viabilidad.xlsx
+++ b/.claude/skills/viabilidad-prerelleno/assets/plantilla_informe_viabilidad.xlsx
@@ -1514,6 +1514,10 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
@@ -1521,6 +1525,10 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C5700"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
@@ -1528,6 +1536,10 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
@@ -9445,13 +9457,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E22:H22">
-    <cfRule type="expression" priority="4" dxfId="3" stopIfTrue="0">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="0">
       <formula>$E$22="verde"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4" stopIfTrue="0">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="0">
       <formula>$E$22="amarillo"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="5" stopIfTrue="0">
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="0">
       <formula>$E$22="rojo"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9459,7 +9471,7 @@
     <dataValidation sqref="E21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"verde,amarillo,rojo"</formula1>
     </dataValidation>
-    <dataValidation sqref="E22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"verde,amarillo,rojo"</formula1>
     </dataValidation>
   </dataValidations>

--- a/.claude/skills/viabilidad-prerelleno/assets/plantilla_informe_viabilidad.xlsx
+++ b/.claude/skills/viabilidad-prerelleno/assets/plantilla_informe_viabilidad.xlsx
@@ -1479,7 +1479,40 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="1"/>
@@ -9423,8 +9456,22 @@
       <formula>$E$21="rojo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <conditionalFormatting sqref="E22:H22">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="0">
+      <formula>$E$22="verde"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="0">
+      <formula>$E$22="amarillo"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="2" stopIfTrue="0">
+      <formula>$E$22="rojo"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
     <dataValidation sqref="E21" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
+      <formula1>"verde,amarillo,rojo"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E22" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"verde,amarillo,rojo"</formula1>
     </dataValidation>
   </dataValidations>

--- a/.claude/skills/viabilidad-prerelleno/assets/plantilla_informe_viabilidad.xlsx
+++ b/.claude/skills/viabilidad-prerelleno/assets/plantilla_informe_viabilidad.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BITACORA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PREGUNTAS'!$B$3:$M$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PREGUNTAS'!$B$3:$M$103</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'AVISOS LLM'!$B$3:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BITACORA'!$B$3:$G$10</definedName>
   </definedNames>
@@ -1387,7 +1387,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -13065,7 +13065,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="1" sort="0"/>
-  <autoFilter ref="B3:M88"/>
+  <autoFilter ref="B3:M103"/>
   <mergeCells count="13">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B54:M54"/>
